--- a/inventory/files/2026-W42/STA_SA_AUTO_2026-W42.xlsx
+++ b/inventory/files/2026-W42/STA_SA_AUTO_2026-W42.xlsx
@@ -1694,7 +1694,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>279</v>
+        <v>304</v>
       </c>
     </row>
     <row r="10">
@@ -1720,21 +1720,21 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AH-RCINT14A1</t>
+          <t>AH-RCPAINTA1</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>79</v>
+        <v>83</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AH-RCPAINTA1</t>
+          <t>AH-RCINT14A1</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>76</v>
+        <v>79</v>
       </c>
     </row>
     <row r="14">
@@ -1744,7 +1744,7 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>31</v>
+        <v>33</v>
       </c>
     </row>
     <row r="15">
@@ -1754,7 +1754,7 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
     </row>
   </sheetData>
